--- a/analysis_outputs/stock_predictions_24m.xlsx
+++ b/analysis_outputs/stock_predictions_24m.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Coding\NSE\stock-options-fetcher\analysis_outputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E261C8F-DEE3-49E1-B398-024C99CA14EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53880" yWindow="-3885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="27">
   <si>
     <t>Symbol</t>
   </si>
@@ -61,29 +55,53 @@
     <t>Samples</t>
   </si>
   <si>
+    <t>PGEL</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>BAJFINANCE</t>
+  </si>
+  <si>
+    <t>UNITDSPR</t>
+  </si>
+  <si>
     <t>PFC</t>
   </si>
   <si>
+    <t>MAZDOCK</t>
+  </si>
+  <si>
     <t>TATACONSUM</t>
   </si>
   <si>
-    <t>ETERNAL</t>
-  </si>
-  <si>
-    <t>RVNL</t>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>NAUKRI</t>
+  </si>
+  <si>
+    <t>HAVELLS</t>
+  </si>
+  <si>
+    <t>CYIENT</t>
+  </si>
+  <si>
+    <t>Decrease</t>
   </si>
   <si>
     <t>Increase</t>
-  </si>
-  <si>
-    <t>Decrease</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,21 +173,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -207,7 +217,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -241,7 +251,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -276,10 +285,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -452,23 +460,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" customWidth="1"/>
-    <col min="7" max="7" width="26.6640625" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" customWidth="1"/>
-    <col min="9" max="9" width="33.6640625" customWidth="1"/>
-    <col min="10" max="10" width="20.6640625" customWidth="1"/>
-    <col min="11" max="11" width="22.6640625" customWidth="1"/>
-    <col min="12" max="12" width="24.6640625" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" customWidth="1"/>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="33.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,168 +517,496 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2">
-        <v>45155</v>
+        <v>45169</v>
       </c>
       <c r="C2" s="2">
-        <v>45886</v>
+        <v>45900</v>
       </c>
       <c r="D2" s="2">
-        <v>0.58019322927459704</v>
+        <v>0.4924883383112383</v>
       </c>
       <c r="E2" s="2">
-        <v>0.41980677072540301</v>
+        <v>0.5075116616887618</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G2" s="2">
-        <v>0.58019322927459704</v>
+        <v>0.5075116616887618</v>
       </c>
       <c r="H2" s="2">
-        <v>-0.2316846045101042</v>
+        <v>-4.569598939264917</v>
       </c>
       <c r="I2" s="2">
-        <v>12.24243167399784</v>
+        <v>34.45890212035604</v>
       </c>
       <c r="J2" s="2">
-        <v>7.5907496263927046</v>
+        <v>31.54300333442077</v>
       </c>
       <c r="K2" s="2">
-        <v>15.942928039702229</v>
+        <v>32.261853090612</v>
       </c>
       <c r="L2" s="2">
-        <v>-15.89211215678665</v>
+        <v>-30.10290478051322</v>
       </c>
       <c r="M2" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="2">
-        <v>45155</v>
+        <v>45169</v>
       </c>
       <c r="C3" s="2">
-        <v>45886</v>
+        <v>45900</v>
       </c>
       <c r="D3" s="2">
-        <v>0.40874120498902872</v>
+        <v>0.7435508646431336</v>
       </c>
       <c r="E3" s="2">
-        <v>0.59125879501097134</v>
+        <v>0.2564491353568665</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2">
-        <v>0.59125879501097134</v>
+        <v>0.7435508646431336</v>
       </c>
       <c r="H3" s="2">
-        <v>0.44310298314133217</v>
+        <v>7.478937974096326</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9834303382465652</v>
+        <v>17.67477603481351</v>
       </c>
       <c r="J3" s="2">
-        <v>3.2281365582867658</v>
+        <v>6.200576198247447</v>
       </c>
       <c r="K3" s="2">
-        <v>9.1843888759055794</v>
+        <v>23.99848110879057</v>
       </c>
       <c r="L3" s="2">
-        <v>-6.262833675564683</v>
+        <v>-14.76387948544346</v>
       </c>
       <c r="M3" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>45155</v>
+        <v>45169</v>
       </c>
       <c r="C4" s="2">
-        <v>45886</v>
+        <v>45900</v>
       </c>
       <c r="D4" s="2">
-        <v>0.69550369842470083</v>
+        <v>0.4504452139038367</v>
       </c>
       <c r="E4" s="2">
-        <v>0.30449630157529922</v>
+        <v>0.5495547860961633</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2">
-        <v>0.69550369842470083</v>
+        <v>0.5495547860961633</v>
       </c>
       <c r="H4" s="2">
-        <v>5.5170849724090187</v>
+        <v>1.410972699703705</v>
       </c>
       <c r="I4" s="2">
-        <v>17.125264263485661</v>
+        <v>31.73049011009827</v>
       </c>
       <c r="J4" s="2">
-        <v>6.8689287206283103</v>
+        <v>7.666242582500534</v>
       </c>
       <c r="K4" s="2">
-        <v>21.47577092511013</v>
+        <v>14.83099596603901</v>
       </c>
       <c r="L4" s="2">
-        <v>-11.93677960181628</v>
+        <v>-10.67098817358603</v>
       </c>
       <c r="M4" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="2">
-        <v>45155</v>
+        <v>45169</v>
       </c>
       <c r="C5" s="2">
-        <v>45886</v>
+        <v>45900</v>
       </c>
       <c r="D5" s="2">
-        <v>0.30391679476207017</v>
+        <v>0.2788020783224907</v>
       </c>
       <c r="E5" s="2">
-        <v>0.69608320523792988</v>
+        <v>0.7211979216775094</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.7211979216775094</v>
+      </c>
+      <c r="H5" s="2">
+        <v>-0.5242620213452903</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.785614773179875</v>
+      </c>
+      <c r="J5" s="2">
+        <v>5.346406937814161</v>
+      </c>
+      <c r="K5" s="2">
+        <v>15.06242151141315</v>
+      </c>
+      <c r="L5" s="2">
+        <v>-9.638875909485344</v>
+      </c>
+      <c r="M5" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.3900877409855681</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.6099122590144319</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.6099122590144319</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-0.4914017976558693</v>
+      </c>
+      <c r="I6" s="2">
+        <v>12.76009353307101</v>
+      </c>
+      <c r="J6" s="2">
+        <v>6.802216100754041</v>
+      </c>
+      <c r="K6" s="2">
+        <v>26.5253050610122</v>
+      </c>
+      <c r="L6" s="2">
+        <v>-20.07462686567164</v>
+      </c>
+      <c r="M6" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="2">
-        <v>0.69608320523792988</v>
-      </c>
-      <c r="H5" s="2">
-        <v>-0.64113856075542142</v>
-      </c>
-      <c r="I5" s="2">
-        <v>18.696347471250029</v>
-      </c>
-      <c r="J5" s="2">
-        <v>8.4736924159503886</v>
-      </c>
-      <c r="K5" s="2">
-        <v>43.063028439661807</v>
-      </c>
-      <c r="L5" s="2">
-        <v>-18.27003513468296</v>
-      </c>
-      <c r="M5" s="2">
+      <c r="B7" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.2824222249329009</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.7175777750670991</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.7175777750670991</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1.609213628774136</v>
+      </c>
+      <c r="I7" s="2">
+        <v>27.78221768474765</v>
+      </c>
+      <c r="J7" s="2">
+        <v>10.01862944343461</v>
+      </c>
+      <c r="K7" s="2">
+        <v>32.19779535405118</v>
+      </c>
+      <c r="L7" s="2">
+        <v>-18.37927844588343</v>
+      </c>
+      <c r="M7" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.4531785339686862</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.5468214660313138</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.5468214660313138</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-0.2248275576152279</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.764571087601311</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4.689845297174446</v>
+      </c>
+      <c r="K8" s="2">
+        <v>13.50318471337582</v>
+      </c>
+      <c r="L8" s="2">
+        <v>-11.56704210870681</v>
+      </c>
+      <c r="M8" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.6962386648879277</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.3037613351120723</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.6962386648879277</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1.036219264778508</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.563113201573017</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4.080905862388482</v>
+      </c>
+      <c r="K9" s="2">
+        <v>10.87155125159875</v>
+      </c>
+      <c r="L9" s="2">
+        <v>-15.25478603603604</v>
+      </c>
+      <c r="M9" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C10" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.506503888758532</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.493496111241468</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.506503888758532</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.07259585948722554</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.7856090765464</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4.265111800168662</v>
+      </c>
+      <c r="K10" s="2">
+        <v>12.24972410531295</v>
+      </c>
+      <c r="L10" s="2">
+        <v>-12.50819457191558</v>
+      </c>
+      <c r="M10" s="2">
         <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.6496120643141187</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.3503879356858813</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.6496120643141187</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1057472862197504</v>
+      </c>
+      <c r="I11" s="2">
+        <v>37.87098563617351</v>
+      </c>
+      <c r="J11" s="2">
+        <v>7.914898259521156</v>
+      </c>
+      <c r="K11" s="2">
+        <v>13.48376964587244</v>
+      </c>
+      <c r="L11" s="2">
+        <v>-18.00845280304198</v>
+      </c>
+      <c r="M11" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C12" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.5654763858761108</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.4345236141238892</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.5654763858761108</v>
+      </c>
+      <c r="H12" s="2">
+        <v>-0.01387099271535119</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.614558477463028</v>
+      </c>
+      <c r="J12" s="2">
+        <v>7.023918229388696</v>
+      </c>
+      <c r="K12" s="2">
+        <v>16.29523490137497</v>
+      </c>
+      <c r="L12" s="2">
+        <v>-16.56026260694254</v>
+      </c>
+      <c r="M12" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45169</v>
+      </c>
+      <c r="C13" s="2">
+        <v>45900</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.4502217827235447</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.5497782172764553</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.5497782172764553</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.01537578319300442</v>
+      </c>
+      <c r="I13" s="2">
+        <v>13.74455215619653</v>
+      </c>
+      <c r="J13" s="2">
+        <v>6.952615397087207</v>
+      </c>
+      <c r="K13" s="2">
+        <v>14.08704022697336</v>
+      </c>
+      <c r="L13" s="2">
+        <v>-13.9262586398622</v>
+      </c>
+      <c r="M13" s="2">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
